--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/19.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/19.xlsx
@@ -426,13 +426,13 @@
         <v>-14.39708942922924</v>
       </c>
       <c r="E2">
-        <v>-22.52757982743895</v>
+        <v>-22.49142449096171</v>
       </c>
       <c r="F2">
-        <v>-3.380765497881559</v>
+        <v>-3.170439700841154</v>
       </c>
       <c r="G2">
-        <v>-15.34140607536719</v>
+        <v>-13.38950580630032</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.68835797497648</v>
       </c>
       <c r="E3">
-        <v>-22.07399881388267</v>
+        <v>-23.28845403020773</v>
       </c>
       <c r="F3">
-        <v>-3.399876762231547</v>
+        <v>-3.363431909977979</v>
       </c>
       <c r="G3">
-        <v>-14.91731639186286</v>
+        <v>-12.70086599395498</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.89186574876598</v>
       </c>
       <c r="E4">
-        <v>-22.45672279464094</v>
+        <v>-23.27542108201365</v>
       </c>
       <c r="F4">
-        <v>-3.217500909728999</v>
+        <v>-3.041173796001694</v>
       </c>
       <c r="G4">
-        <v>-14.925396399953</v>
+        <v>-13.79203130171598</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.97651228428743</v>
       </c>
       <c r="E5">
-        <v>-23.32899292952439</v>
+        <v>-24.659490292296</v>
       </c>
       <c r="F5">
-        <v>-3.383770814818916</v>
+        <v>-2.970714521454373</v>
       </c>
       <c r="G5">
-        <v>-15.04222757479859</v>
+        <v>-13.30238937389706</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.97262873096093</v>
       </c>
       <c r="E6">
-        <v>-23.91660318828569</v>
+        <v>-23.81882437751207</v>
       </c>
       <c r="F6">
-        <v>-3.14007672205894</v>
+        <v>-2.429825398857214</v>
       </c>
       <c r="G6">
-        <v>-14.98928178371539</v>
+        <v>-13.71254206882765</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.91074515506366</v>
       </c>
       <c r="E7">
-        <v>-23.88249925053393</v>
+        <v>-26.07305798226431</v>
       </c>
       <c r="F7">
-        <v>-3.136894962864788</v>
+        <v>-2.846173624280481</v>
       </c>
       <c r="G7">
-        <v>-14.8217130798961</v>
+        <v>-13.25395854367965</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.81749460452057</v>
       </c>
       <c r="E8">
-        <v>-24.76362708057638</v>
+        <v>-25.87853738126483</v>
       </c>
       <c r="F8">
-        <v>-2.969051988076954</v>
+        <v>-2.906780296938904</v>
       </c>
       <c r="G8">
-        <v>-14.39429131589816</v>
+        <v>-12.95644362244168</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.72486539050368</v>
       </c>
       <c r="E9">
-        <v>-25.29101769198368</v>
+        <v>-25.17652428364775</v>
       </c>
       <c r="F9">
-        <v>-2.857331733196191</v>
+        <v>-2.378043324140814</v>
       </c>
       <c r="G9">
-        <v>-14.18617163543648</v>
+        <v>-13.72639538625162</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.65769779449034</v>
       </c>
       <c r="E10">
-        <v>-26.29871637054053</v>
+        <v>-25.27612354097245</v>
       </c>
       <c r="F10">
-        <v>-2.702946415234238</v>
+        <v>-1.956357099173906</v>
       </c>
       <c r="G10">
-        <v>-13.56251805668672</v>
+        <v>-14.12514747687392</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.62587906206595</v>
       </c>
       <c r="E11">
-        <v>-26.05063750745233</v>
+        <v>-27.38892384551713</v>
       </c>
       <c r="F11">
-        <v>-2.949969716586065</v>
+        <v>-2.371534013089615</v>
       </c>
       <c r="G11">
-        <v>-13.49707409268359</v>
+        <v>-12.82987706322922</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.64546701899432</v>
       </c>
       <c r="E12">
-        <v>-26.85410200826324</v>
+        <v>-26.52606840809562</v>
       </c>
       <c r="F12">
-        <v>-2.793460464603335</v>
+        <v>-2.196090767381097</v>
       </c>
       <c r="G12">
-        <v>-13.49375349646544</v>
+        <v>-13.90565836370877</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.70666374078081</v>
       </c>
       <c r="E13">
-        <v>-27.48376820513377</v>
+        <v>-26.86413710666424</v>
       </c>
       <c r="F13">
-        <v>-2.712993683462794</v>
+        <v>-1.238610707711649</v>
       </c>
       <c r="G13">
-        <v>-13.03498950413167</v>
+        <v>-12.9228012577927</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.80492127658071</v>
       </c>
       <c r="E14">
-        <v>-27.72210179215747</v>
+        <v>-29.55236833912658</v>
       </c>
       <c r="F14">
-        <v>-2.518497987489887</v>
+        <v>-1.897869390331844</v>
       </c>
       <c r="G14">
-        <v>-12.59596862192109</v>
+        <v>-13.55911214870801</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.92328527280482</v>
       </c>
       <c r="E15">
-        <v>-28.9124564698137</v>
+        <v>-28.96668494605555</v>
       </c>
       <c r="F15">
-        <v>-2.330471840932844</v>
+        <v>-1.127733730846935</v>
       </c>
       <c r="G15">
-        <v>-11.63543038505236</v>
+        <v>-11.73701044208965</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.03275263947791</v>
       </c>
       <c r="E16">
-        <v>-28.46459491892911</v>
+        <v>-29.96211598852562</v>
       </c>
       <c r="F16">
-        <v>-2.268461085526675</v>
+        <v>-0.7885156226657319</v>
       </c>
       <c r="G16">
-        <v>-11.80400314266883</v>
+        <v>-11.85808095519004</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-15.11092255248206</v>
       </c>
       <c r="E17">
-        <v>-30.16119223437681</v>
+        <v>-30.58799185265173</v>
       </c>
       <c r="F17">
-        <v>-1.975717702112136</v>
+        <v>-1.55083646407263</v>
       </c>
       <c r="G17">
-        <v>-11.15849498772239</v>
+        <v>-11.78608111051115</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-15.12417714195039</v>
       </c>
       <c r="E18">
-        <v>-30.27304554236627</v>
+        <v>-30.79489556582518</v>
       </c>
       <c r="F18">
-        <v>-2.036504130496966</v>
+        <v>-0.7278807855156137</v>
       </c>
       <c r="G18">
-        <v>-11.11381459374743</v>
+        <v>-12.02215187682696</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.05076302975869</v>
       </c>
       <c r="E19">
-        <v>-32.04081235531853</v>
+        <v>-31.73742723917465</v>
       </c>
       <c r="F19">
-        <v>-1.606613754772732</v>
+        <v>-0.5656707090668174</v>
       </c>
       <c r="G19">
-        <v>-10.64513146863947</v>
+        <v>-10.54368594168612</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.87716579391356</v>
       </c>
       <c r="E20">
-        <v>-31.51791851860084</v>
+        <v>-31.60730380280125</v>
       </c>
       <c r="F20">
-        <v>-1.63416111275283</v>
+        <v>0.04726235491921804</v>
       </c>
       <c r="G20">
-        <v>-10.5730003750982</v>
+        <v>-10.40091999163468</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-14.58928937120112</v>
       </c>
       <c r="E21">
-        <v>-32.43121436375679</v>
+        <v>-34.54603210347188</v>
       </c>
       <c r="F21">
-        <v>-1.435215427092084</v>
+        <v>-0.670053285493583</v>
       </c>
       <c r="G21">
-        <v>-10.82424350990488</v>
+        <v>-11.37964932082897</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-14.19408622162128</v>
       </c>
       <c r="E22">
-        <v>-33.28092137689703</v>
+        <v>-32.04880964041607</v>
       </c>
       <c r="F22">
-        <v>-1.474319338708637</v>
+        <v>0.2983869032823049</v>
       </c>
       <c r="G22">
-        <v>-10.02878352969181</v>
+        <v>-10.59975873691547</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-13.69902326955356</v>
       </c>
       <c r="E23">
-        <v>-33.68497447023142</v>
+        <v>-34.0061361110924</v>
       </c>
       <c r="F23">
-        <v>-1.415669269855626</v>
+        <v>1.056533601346497</v>
       </c>
       <c r="G23">
-        <v>-10.25510906797607</v>
+        <v>-9.69814139558969</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.12503107402568</v>
       </c>
       <c r="E24">
-        <v>-34.07467230096149</v>
+        <v>-34.4541788009373</v>
       </c>
       <c r="F24">
-        <v>-1.119970271547898</v>
+        <v>1.02508380453181</v>
       </c>
       <c r="G24">
-        <v>-10.13003546457316</v>
+        <v>-9.243656116169443</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.50701203195144</v>
       </c>
       <c r="E25">
-        <v>-34.05456361213043</v>
+        <v>-35.24926336059702</v>
       </c>
       <c r="F25">
-        <v>-1.145574279601028</v>
+        <v>0.4145662598923384</v>
       </c>
       <c r="G25">
-        <v>-9.972943701193184</v>
+        <v>-9.653815373543152</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.87097304224763</v>
       </c>
       <c r="E26">
-        <v>-34.64928810355778</v>
+        <v>-36.12249806044411</v>
       </c>
       <c r="F26">
-        <v>-0.9866685607219989</v>
+        <v>0.9022766803319782</v>
       </c>
       <c r="G26">
-        <v>-9.639640496406351</v>
+        <v>-10.85936570547718</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.26016181144166</v>
       </c>
       <c r="E27">
-        <v>-34.25053785328637</v>
+        <v>-34.51713138235493</v>
       </c>
       <c r="F27">
-        <v>-1.067685377817999</v>
+        <v>0.828358143510567</v>
       </c>
       <c r="G27">
-        <v>-9.919223541821957</v>
+        <v>-9.30400106186919</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.70584337694433</v>
       </c>
       <c r="E28">
-        <v>-34.42043034839514</v>
+        <v>-34.34937179850377</v>
       </c>
       <c r="F28">
-        <v>-0.9698957775501145</v>
+        <v>0.6842288423626754</v>
       </c>
       <c r="G28">
-        <v>-10.07982621227054</v>
+        <v>-10.71779412007337</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.23371731679762</v>
       </c>
       <c r="E29">
-        <v>-33.79151814244688</v>
+        <v>-35.23848559245877</v>
       </c>
       <c r="F29">
-        <v>-1.027435005715971</v>
+        <v>0.2963673435542798</v>
       </c>
       <c r="G29">
-        <v>-9.91849511063576</v>
+        <v>-9.96115755335166</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.868454031822678</v>
       </c>
       <c r="E30">
-        <v>-34.13851246328462</v>
+        <v>-35.34366392976091</v>
       </c>
       <c r="F30">
-        <v>-1.079196371247301</v>
+        <v>0.7392307811737571</v>
       </c>
       <c r="G30">
-        <v>-9.811159790983204</v>
+        <v>-8.859142886504355</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.610994920711651</v>
       </c>
       <c r="E31">
-        <v>-34.2840893172092</v>
+        <v>-34.07754335348235</v>
       </c>
       <c r="F31">
-        <v>-1.02233060577992</v>
+        <v>0.622748242094299</v>
       </c>
       <c r="G31">
-        <v>-10.34258643475087</v>
+        <v>-9.197023395366616</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.462325823826292</v>
       </c>
       <c r="E32">
-        <v>-33.70143320901229</v>
+        <v>-35.04755833558437</v>
       </c>
       <c r="F32">
-        <v>-1.005817929972515</v>
+        <v>1.057849048782142</v>
       </c>
       <c r="G32">
-        <v>-10.19366491305391</v>
+        <v>-9.279680647670586</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.409710696776184</v>
       </c>
       <c r="E33">
-        <v>-33.13121681891446</v>
+        <v>-35.96524227205375</v>
       </c>
       <c r="F33">
-        <v>-0.9394102003922871</v>
+        <v>0.2395711609487345</v>
       </c>
       <c r="G33">
-        <v>-9.683139650619909</v>
+        <v>-9.21051905964061</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.426426932158151</v>
       </c>
       <c r="E34">
-        <v>-32.93060768461167</v>
+        <v>-33.36885302094097</v>
       </c>
       <c r="F34">
-        <v>-1.063174088942353</v>
+        <v>0.6606377670983483</v>
       </c>
       <c r="G34">
-        <v>-10.12389301781388</v>
+        <v>-9.903194774504069</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.490085766639648</v>
       </c>
       <c r="E35">
-        <v>-32.66687615111596</v>
+        <v>-32.36340499396594</v>
       </c>
       <c r="F35">
-        <v>-1.196851878569123</v>
+        <v>-0.1301424647991297</v>
       </c>
       <c r="G35">
-        <v>-10.38759495088177</v>
+        <v>-9.727278643037559</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.567741355262212</v>
       </c>
       <c r="E36">
-        <v>-32.40198079980028</v>
+        <v>-34.28927668418499</v>
       </c>
       <c r="F36">
-        <v>-1.163283946305479</v>
+        <v>-0.3167405059537463</v>
       </c>
       <c r="G36">
-        <v>-10.18532732907136</v>
+        <v>-8.890298085211283</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.631117449223417</v>
       </c>
       <c r="E37">
-        <v>-32.15087691607496</v>
+        <v>-33.09884502247063</v>
       </c>
       <c r="F37">
-        <v>-1.118050944275612</v>
+        <v>0.2683942047291433</v>
       </c>
       <c r="G37">
-        <v>-10.19324163547274</v>
+        <v>-9.177283566464995</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.660800521560764</v>
       </c>
       <c r="E38">
-        <v>-31.76457770508764</v>
+        <v>-33.07206589142627</v>
       </c>
       <c r="F38">
-        <v>-1.003060294888596</v>
+        <v>-0.207340508168224</v>
       </c>
       <c r="G38">
-        <v>-10.27528858056666</v>
+        <v>-8.325973914088623</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.634466079753643</v>
       </c>
       <c r="E39">
-        <v>-31.30559195780321</v>
+        <v>-31.31998571243658</v>
       </c>
       <c r="F39">
-        <v>-0.9484650844722885</v>
+        <v>0.1908672995011375</v>
       </c>
       <c r="G39">
-        <v>-10.36085627639386</v>
+        <v>-8.201221870398536</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.549434210988101</v>
       </c>
       <c r="E40">
-        <v>-31.29635387082756</v>
+        <v>-32.74717052374596</v>
       </c>
       <c r="F40">
-        <v>-1.09019460525427</v>
+        <v>0.1193493714130394</v>
       </c>
       <c r="G40">
-        <v>-10.66324381164761</v>
+        <v>-8.294831840267934</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.407192891101422</v>
       </c>
       <c r="E41">
-        <v>-29.98681202152645</v>
+        <v>-30.54215237450909</v>
       </c>
       <c r="F41">
-        <v>-0.9205259087106668</v>
+        <v>0.2286416814361978</v>
       </c>
       <c r="G41">
-        <v>-10.7043050182425</v>
+        <v>-8.340808316758872</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.216215917205384</v>
       </c>
       <c r="E42">
-        <v>-29.87306128292778</v>
+        <v>-29.75957319582155</v>
       </c>
       <c r="F42">
-        <v>-0.905804163228114</v>
+        <v>-0.4883177609933995</v>
       </c>
       <c r="G42">
-        <v>-10.5967301694161</v>
+        <v>-8.356318651070367</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.995816050071266</v>
       </c>
       <c r="E43">
-        <v>-29.50897650118509</v>
+        <v>-31.22106119773903</v>
       </c>
       <c r="F43">
-        <v>-0.9927446356215333</v>
+        <v>-0.2298803851983986</v>
       </c>
       <c r="G43">
-        <v>-10.51217965227233</v>
+        <v>-9.124068715213921</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.758631836405323</v>
       </c>
       <c r="E44">
-        <v>-29.06866165223428</v>
+        <v>-29.71926298444227</v>
       </c>
       <c r="F44">
-        <v>-0.8902706176908176</v>
+        <v>0.2887024599761759</v>
       </c>
       <c r="G44">
-        <v>-9.960409434836107</v>
+        <v>-8.792468464416437</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.52448966445532</v>
       </c>
       <c r="E45">
-        <v>-28.06651488281084</v>
+        <v>-28.99642796333793</v>
       </c>
       <c r="F45">
-        <v>-1.025324325573638</v>
+        <v>-0.1650018218437385</v>
       </c>
       <c r="G45">
-        <v>-10.67829477494078</v>
+        <v>-8.513771348821882</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.310767489749018</v>
       </c>
       <c r="E46">
-        <v>-27.58736610500725</v>
+        <v>-28.07951160321285</v>
       </c>
       <c r="F46">
-        <v>-0.9237383174987233</v>
+        <v>0.3446288568087817</v>
       </c>
       <c r="G46">
-        <v>-10.27130189637193</v>
+        <v>-9.002591330640159</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.127299786423869</v>
       </c>
       <c r="E47">
-        <v>-27.47475654185851</v>
+        <v>-27.52028129105762</v>
       </c>
       <c r="F47">
-        <v>-0.9376722855812137</v>
+        <v>0.2153762058477665</v>
       </c>
       <c r="G47">
-        <v>-11.09415023294168</v>
+        <v>-9.113870678607167</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.986337239092452</v>
       </c>
       <c r="E48">
-        <v>-27.41975369656135</v>
+        <v>-28.29316953536874</v>
       </c>
       <c r="F48">
-        <v>-0.7553113436919165</v>
+        <v>0.1397106421738513</v>
       </c>
       <c r="G48">
-        <v>-10.90431515962001</v>
+        <v>-8.234437676244793</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.889538568769496</v>
       </c>
       <c r="E49">
-        <v>-26.17648380012549</v>
+        <v>-27.0692724507377</v>
       </c>
       <c r="F49">
-        <v>-0.9197828631503556</v>
+        <v>0.4770044528783511</v>
       </c>
       <c r="G49">
-        <v>-10.58771337257075</v>
+        <v>-8.102338977483109</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.835385686492182</v>
       </c>
       <c r="E50">
-        <v>-26.11369197953513</v>
+        <v>-26.27301275207299</v>
       </c>
       <c r="F50">
-        <v>-0.8232813741938244</v>
+        <v>0.5904825033878555</v>
       </c>
       <c r="G50">
-        <v>-10.69439901035453</v>
+        <v>-8.794998286238769</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.823559488409098</v>
       </c>
       <c r="E51">
-        <v>-25.53181476886754</v>
+        <v>-25.52990828131032</v>
       </c>
       <c r="F51">
-        <v>-0.7114327223656267</v>
+        <v>-0.1147124651871833</v>
       </c>
       <c r="G51">
-        <v>-11.2208578846812</v>
+        <v>-9.345075393350319</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.841694310420149</v>
       </c>
       <c r="E52">
-        <v>-25.53318236801786</v>
+        <v>-25.72013136047652</v>
       </c>
       <c r="F52">
-        <v>-0.7401000330743093</v>
+        <v>0.03494618837439499</v>
       </c>
       <c r="G52">
-        <v>-11.01865588730198</v>
+        <v>-8.955584550579553</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.883121612919425</v>
       </c>
       <c r="E53">
-        <v>-24.50875097800267</v>
+        <v>-25.72290278656921</v>
       </c>
       <c r="F53">
-        <v>-0.808892632407197</v>
+        <v>-0.1639282576897103</v>
       </c>
       <c r="G53">
-        <v>-10.93597566644709</v>
+        <v>-9.341364331766588</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.935924104393026</v>
       </c>
       <c r="E54">
-        <v>-23.77546423888863</v>
+        <v>-26.7548288010671</v>
       </c>
       <c r="F54">
-        <v>-0.8255386753664531</v>
+        <v>0.09411812869116927</v>
       </c>
       <c r="G54">
-        <v>-11.31658424245644</v>
+        <v>-8.172524306639632</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.987696385791075</v>
       </c>
       <c r="E55">
-        <v>-23.19509048159159</v>
+        <v>-24.73383425007992</v>
       </c>
       <c r="F55">
-        <v>-0.9693432564924472</v>
+        <v>-0.7207369450338708</v>
       </c>
       <c r="G55">
-        <v>-11.2651543757337</v>
+        <v>-9.633583361407615</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.034553454030323</v>
       </c>
       <c r="E56">
-        <v>-23.36029827033942</v>
+        <v>-24.63889479250911</v>
       </c>
       <c r="F56">
-        <v>-0.8848464679372865</v>
+        <v>-0.05259319365124836</v>
       </c>
       <c r="G56">
-        <v>-11.34909786688898</v>
+        <v>-10.01721066125165</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.066170840506931</v>
       </c>
       <c r="E57">
-        <v>-23.00891585818824</v>
+        <v>-23.15399457997198</v>
       </c>
       <c r="F57">
-        <v>-1.01340329027995</v>
+        <v>-0.03081292952944096</v>
       </c>
       <c r="G57">
-        <v>-11.64164829990751</v>
+        <v>-9.409771238837891</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.081449226737195</v>
       </c>
       <c r="E58">
-        <v>-22.38083009874639</v>
+        <v>-23.94552655177268</v>
       </c>
       <c r="F58">
-        <v>-0.8958811501099787</v>
+        <v>-0.1047637726795612</v>
       </c>
       <c r="G58">
-        <v>-11.82008112831011</v>
+        <v>-9.90141307119729</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.0805427883052</v>
       </c>
       <c r="E59">
-        <v>-22.05844350566633</v>
+        <v>-22.58560316489923</v>
       </c>
       <c r="F59">
-        <v>-1.030657354912861</v>
+        <v>-0.9354257531848215</v>
       </c>
       <c r="G59">
-        <v>-11.87560267831748</v>
+        <v>-10.00476498787668</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.061861415452745</v>
       </c>
       <c r="E60">
-        <v>-21.66014610279569</v>
+        <v>-22.31495438735681</v>
       </c>
       <c r="F60">
-        <v>-1.030155364266764</v>
+        <v>0.1165875944921059</v>
       </c>
       <c r="G60">
-        <v>-11.84752198421175</v>
+        <v>-10.50505283904522</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.031366166110654</v>
       </c>
       <c r="E61">
-        <v>-21.97762383005144</v>
+        <v>-24.31231936097196</v>
       </c>
       <c r="F61">
-        <v>-1.190645749987349</v>
+        <v>-0.4409699369841854</v>
       </c>
       <c r="G61">
-        <v>-12.08750068540486</v>
+        <v>-10.70329768322375</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.991315725490999</v>
       </c>
       <c r="E62">
-        <v>-21.29762817305965</v>
+        <v>-23.50711139766809</v>
       </c>
       <c r="F62">
-        <v>-1.130522015524758</v>
+        <v>0.5225215849273784</v>
       </c>
       <c r="G62">
-        <v>-11.97449869611914</v>
+        <v>-11.15025912160819</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.945708152459634</v>
       </c>
       <c r="E63">
-        <v>-21.37392390314088</v>
+        <v>-21.29760553068962</v>
       </c>
       <c r="F63">
-        <v>-1.225250798239298</v>
+        <v>-0.8516397038612626</v>
       </c>
       <c r="G63">
-        <v>-12.45440359896041</v>
+        <v>-10.39958125323843</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.902128393907911</v>
       </c>
       <c r="E64">
-        <v>-20.95632161557555</v>
+        <v>-20.75330559733768</v>
       </c>
       <c r="F64">
-        <v>-1.156310749508712</v>
+        <v>-0.4938529119789058</v>
       </c>
       <c r="G64">
-        <v>-12.88571361050629</v>
+        <v>-11.06000256017254</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.859801951642519</v>
       </c>
       <c r="E65">
-        <v>-20.57275986712587</v>
+        <v>-21.35630813925104</v>
       </c>
       <c r="F65">
-        <v>-1.247376491568073</v>
+        <v>-0.9771522759986382</v>
       </c>
       <c r="G65">
-        <v>-12.48796065184885</v>
+        <v>-12.22281826251636</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.82246024125515</v>
       </c>
       <c r="E66">
-        <v>-21.11689677541353</v>
+        <v>-20.80607137647505</v>
       </c>
       <c r="F66">
-        <v>-1.767167924783332</v>
+        <v>0.5689449509150682</v>
       </c>
       <c r="G66">
-        <v>-12.6386540331879</v>
+        <v>-12.05623392516491</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.788073199735915</v>
       </c>
       <c r="E67">
-        <v>-20.5072464336569</v>
+        <v>-21.50468359011236</v>
       </c>
       <c r="F67">
-        <v>-1.671131978307174</v>
+        <v>-1.079336365338374</v>
       </c>
       <c r="G67">
-        <v>-12.1392291432895</v>
+        <v>-10.0361794030868</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.752381765636438</v>
       </c>
       <c r="E68">
-        <v>-20.20008909866463</v>
+        <v>-21.05703034903213</v>
       </c>
       <c r="F68">
-        <v>-1.500509002515546</v>
+        <v>-0.6933809399238199</v>
       </c>
       <c r="G68">
-        <v>-12.57831236870972</v>
+        <v>-11.66115844329997</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.71499229481505</v>
       </c>
       <c r="E69">
-        <v>-20.04492093679181</v>
+        <v>-21.81403270652434</v>
       </c>
       <c r="F69">
-        <v>-1.49784414458074</v>
+        <v>-0.693206982769232</v>
       </c>
       <c r="G69">
-        <v>-12.64865847772265</v>
+        <v>-11.96113756192908</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.665900448236781</v>
       </c>
       <c r="E70">
-        <v>-20.24703126022814</v>
+        <v>-20.20687275272812</v>
       </c>
       <c r="F70">
-        <v>-1.76739821092131</v>
+        <v>-1.574968463250985</v>
       </c>
       <c r="G70">
-        <v>-12.68858766287953</v>
+        <v>-11.44817107065485</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.603338933123956</v>
       </c>
       <c r="E71">
-        <v>-20.31725430666509</v>
+        <v>-19.47537928932112</v>
       </c>
       <c r="F71">
-        <v>-1.828741302200822</v>
+        <v>-0.7825372951197279</v>
       </c>
       <c r="G71">
-        <v>-12.5100760851595</v>
+        <v>-11.71601718655232</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.521152144251066</v>
       </c>
       <c r="E72">
-        <v>-20.10374128567744</v>
+        <v>-21.20702246511419</v>
       </c>
       <c r="F72">
-        <v>-1.848644485787886</v>
+        <v>-1.423325869759702</v>
       </c>
       <c r="G72">
-        <v>-12.21779799353041</v>
+        <v>-10.85583182985765</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.41283914534657</v>
       </c>
       <c r="E73">
-        <v>-20.52274740018516</v>
+        <v>-22.25180481731984</v>
       </c>
       <c r="F73">
-        <v>-1.906791735627397</v>
+        <v>-1.204550725210742</v>
       </c>
       <c r="G73">
-        <v>-11.79020888723293</v>
+        <v>-11.82838261885551</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.277908171876104</v>
       </c>
       <c r="E74">
-        <v>-20.57751023635991</v>
+        <v>-20.105253795996</v>
       </c>
       <c r="F74">
-        <v>-2.074585008371062</v>
+        <v>-1.762128965872103</v>
       </c>
       <c r="G74">
-        <v>-12.50025210781053</v>
+        <v>-10.23719359826151</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.11009594005783</v>
       </c>
       <c r="E75">
-        <v>-20.6624553517958</v>
+        <v>-21.529852848647</v>
       </c>
       <c r="F75">
-        <v>-2.093041862472838</v>
+        <v>-1.31634056295334</v>
       </c>
       <c r="G75">
-        <v>-12.21024790272212</v>
+        <v>-10.75232569576497</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.911860250469857</v>
       </c>
       <c r="E76">
-        <v>-20.87534797184439</v>
+        <v>-20.6498254377884</v>
       </c>
       <c r="F76">
-        <v>-2.011320104717056</v>
+        <v>-1.633423865764338</v>
       </c>
       <c r="G76">
-        <v>-12.24330620993353</v>
+        <v>-10.59693688637435</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.686241295655694</v>
       </c>
       <c r="E77">
-        <v>-20.64352633044373</v>
+        <v>-20.96457702369153</v>
       </c>
       <c r="F77">
-        <v>-2.149493444238819</v>
+        <v>-1.806446621921876</v>
       </c>
       <c r="G77">
-        <v>-11.74057056748165</v>
+        <v>-10.29082516465063</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.435046851988671</v>
       </c>
       <c r="E78">
-        <v>-21.27167096004769</v>
+        <v>-22.13928582365126</v>
       </c>
       <c r="F78">
-        <v>-2.011681272904676</v>
+        <v>-1.656927134083968</v>
       </c>
       <c r="G78">
-        <v>-11.14873991602616</v>
+        <v>-10.05350753414223</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.167354393860381</v>
       </c>
       <c r="E79">
-        <v>-21.81296398665853</v>
+        <v>-20.79554720288123</v>
       </c>
       <c r="F79">
-        <v>-2.385992337738078</v>
+        <v>-1.774632343449959</v>
       </c>
       <c r="G79">
-        <v>-11.20557067343575</v>
+        <v>-10.3517180743508</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.887429804389199</v>
       </c>
       <c r="E80">
-        <v>-21.98872764831824</v>
+        <v>-22.21300485202212</v>
       </c>
       <c r="F80">
-        <v>-2.195578007958764</v>
+        <v>-2.143539139347496</v>
       </c>
       <c r="G80">
-        <v>-10.57087414352768</v>
+        <v>-10.29803728963829</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.603308485621413</v>
       </c>
       <c r="E81">
-        <v>-23.01337187661179</v>
+        <v>-23.13888306220838</v>
       </c>
       <c r="F81">
-        <v>-2.247533211462349</v>
+        <v>-1.698205510132871</v>
       </c>
       <c r="G81">
-        <v>-10.28914517921219</v>
+        <v>-9.471671483556817</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.324757989648709</v>
       </c>
       <c r="E82">
-        <v>-23.13761961796024</v>
+        <v>-22.41368417767204</v>
       </c>
       <c r="F82">
-        <v>-2.268900948617562</v>
+        <v>-1.721009636364538</v>
       </c>
       <c r="G82">
-        <v>-10.46274804947929</v>
+        <v>-9.33928075607634</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.055188256053292</v>
       </c>
       <c r="E83">
-        <v>-23.56262143205411</v>
+        <v>-24.94296823670215</v>
       </c>
       <c r="F83">
-        <v>-2.4967533431664</v>
+        <v>-2.171431926534561</v>
       </c>
       <c r="G83">
-        <v>-9.948436257365692</v>
+        <v>-8.082943676845231</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.805448050235485</v>
       </c>
       <c r="E84">
-        <v>-24.32203293771841</v>
+        <v>-25.87347454732425</v>
       </c>
       <c r="F84">
-        <v>-2.383591729004765</v>
+        <v>-2.130290231107121</v>
       </c>
       <c r="G84">
-        <v>-9.966610943583456</v>
+        <v>-8.263981795166034</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.579654208608845</v>
       </c>
       <c r="E85">
-        <v>-25.60674742827247</v>
+        <v>-25.57968979607664</v>
       </c>
       <c r="F85">
-        <v>-2.588514085476709</v>
+        <v>-2.653217863309379</v>
       </c>
       <c r="G85">
-        <v>-9.557308085036764</v>
+        <v>-7.684114477516286</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.381432856125045</v>
       </c>
       <c r="E86">
-        <v>-26.53924626745794</v>
+        <v>-27.58476223245284</v>
       </c>
       <c r="F86">
-        <v>-2.581555799293193</v>
+        <v>-2.179116690930332</v>
       </c>
       <c r="G86">
-        <v>-9.002565080867683</v>
+        <v>-8.05139473155117</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.216078149411373</v>
       </c>
       <c r="E87">
-        <v>-26.97592248754358</v>
+        <v>-26.61350418423572</v>
       </c>
       <c r="F87">
-        <v>-2.645548009526858</v>
+        <v>-2.741565731920154</v>
       </c>
       <c r="G87">
-        <v>-8.800353239823783</v>
+        <v>-8.447864732578875</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.081862816888531</v>
       </c>
       <c r="E88">
-        <v>-28.37057474158185</v>
+        <v>-29.0391541156003</v>
       </c>
       <c r="F88">
-        <v>-2.64896916690042</v>
+        <v>-1.969810614162772</v>
       </c>
       <c r="G88">
-        <v>-9.249152162281513</v>
+        <v>-7.959937243024768</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.981533520788952</v>
       </c>
       <c r="E89">
-        <v>-29.21079686591303</v>
+        <v>-28.77574636799614</v>
       </c>
       <c r="F89">
-        <v>-2.934343393899655</v>
+        <v>-2.081726363750597</v>
       </c>
       <c r="G89">
-        <v>-8.704456258527452</v>
+        <v>-8.040743886369214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.916577162547425</v>
       </c>
       <c r="E90">
-        <v>-31.18595873146857</v>
+        <v>-31.65105791866336</v>
       </c>
       <c r="F90">
-        <v>-3.034475617182657</v>
+        <v>-2.339110056209237</v>
       </c>
       <c r="G90">
-        <v>-8.615531873044942</v>
+        <v>-6.167419029986357</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.885516206268666</v>
       </c>
       <c r="E91">
-        <v>-32.57065287116397</v>
+        <v>-32.7283569784811</v>
       </c>
       <c r="F91">
-        <v>-3.084273751969352</v>
+        <v>-2.957128467681058</v>
       </c>
       <c r="G91">
-        <v>-8.441105416166419</v>
+        <v>-6.890777447652183</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.891064104260877</v>
       </c>
       <c r="E92">
-        <v>-33.28114780059742</v>
+        <v>-33.93937281879732</v>
       </c>
       <c r="F92">
-        <v>-3.103824879410226</v>
+        <v>-2.425805331851428</v>
       </c>
       <c r="G92">
-        <v>-8.121540686048979</v>
+        <v>-6.549494312032778</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.931979161626491</v>
       </c>
       <c r="E93">
-        <v>-35.58071369440344</v>
+        <v>-35.68571768545629</v>
       </c>
       <c r="F93">
-        <v>-3.183001064137205</v>
+        <v>-2.715540913226402</v>
       </c>
       <c r="G93">
-        <v>-8.681120210796681</v>
+        <v>-7.397709772478595</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.005983589132503</v>
       </c>
       <c r="E94">
-        <v>-37.11997597316564</v>
+        <v>-36.21698693485116</v>
       </c>
       <c r="F94">
-        <v>-3.587635346117485</v>
+        <v>-2.996277111137363</v>
       </c>
       <c r="G94">
-        <v>-8.57742704707511</v>
+        <v>-6.587087267439337</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.113462050182603</v>
       </c>
       <c r="E95">
-        <v>-38.25701239785556</v>
+        <v>-37.40771974008702</v>
       </c>
       <c r="F95">
-        <v>-3.580310093174529</v>
+        <v>-3.06792177943809</v>
       </c>
       <c r="G95">
-        <v>-9.677604229849125</v>
+        <v>-6.94982631083595</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.248823142510853</v>
       </c>
       <c r="E96">
-        <v>-40.27671180527654</v>
+        <v>-42.5758859860809</v>
       </c>
       <c r="F96">
-        <v>-3.799998926968778</v>
+        <v>-3.71815125736777</v>
       </c>
       <c r="G96">
-        <v>-9.628234970265721</v>
+        <v>-6.874269621986617</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.405449568006874</v>
       </c>
       <c r="E97">
-        <v>-41.8946993404251</v>
+        <v>-42.26863128889747</v>
       </c>
       <c r="F97">
-        <v>-3.83090614313463</v>
+        <v>-3.361950789061774</v>
       </c>
       <c r="G97">
-        <v>-9.85136131752952</v>
+        <v>-7.033553241368301</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.579221459439756</v>
       </c>
       <c r="E98">
-        <v>-43.29957462453569</v>
+        <v>-44.33924885806069</v>
       </c>
       <c r="F98">
-        <v>-3.807454233593973</v>
+        <v>-3.262831659112396</v>
       </c>
       <c r="G98">
-        <v>-9.471445079269214</v>
+        <v>-7.411471215698906</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.753108841034375</v>
       </c>
       <c r="E99">
-        <v>-45.62908278848042</v>
+        <v>-44.78430501929753</v>
       </c>
       <c r="F99">
-        <v>-3.94081144503586</v>
+        <v>-3.828922203204925</v>
       </c>
       <c r="G99">
-        <v>-9.95524479210154</v>
+        <v>-7.519006689866587</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.926093650337775</v>
       </c>
       <c r="E100">
-        <v>-47.85676595012568</v>
+        <v>-48.5825931604306</v>
       </c>
       <c r="F100">
-        <v>-4.201349560564361</v>
+        <v>-3.862536524043127</v>
       </c>
       <c r="G100">
-        <v>-10.84531551475963</v>
+        <v>-7.420898165239191</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.069947559890925</v>
       </c>
       <c r="E101">
-        <v>-49.58382857445999</v>
+        <v>-50.69070649437733</v>
       </c>
       <c r="F101">
-        <v>-4.269904418452645</v>
+        <v>-4.034779786474631</v>
       </c>
       <c r="G101">
-        <v>-10.73928612128774</v>
+        <v>-8.398413442456484</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.193264682509234</v>
       </c>
       <c r="E102">
-        <v>-51.47361398743043</v>
+        <v>-52.84304150912747</v>
       </c>
       <c r="F102">
-        <v>-4.478228051480484</v>
+        <v>-3.957936284353934</v>
       </c>
       <c r="G102">
-        <v>-10.86449097355303</v>
+        <v>-7.914059203180612</v>
       </c>
     </row>
   </sheetData>
